--- a/movie_database.xlsx
+++ b/movie_database.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,6 +519,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>IMDb ID</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IMDb URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -556,6 +567,11 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=2001%3A+A+Space+Odyssey+1968+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -594,6 +610,11 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Godfather+1972+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -632,6 +653,11 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Citizen+Kane+1941+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -670,6 +696,11 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Vertigo+1958+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -708,6 +739,11 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Seven+Samurai+1954+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -746,6 +782,11 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Tokyo+Story+1953+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -784,6 +825,11 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=In+the+Mood+for+Love+2000+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -822,6 +868,11 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Jeanne+Dielman%2C+23+quai+du+Commerce%2C+1080+Bruxelles+1975+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -860,6 +911,11 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Casablanca+1942+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -898,6 +954,11 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Apocalypse+Now+1979+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -936,6 +997,11 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Singin%E2%80%99+in+the+Rain+1952+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -974,6 +1040,11 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Mulholland+Drive+2001+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1012,6 +1083,11 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=North+by+Northwest+1959+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1050,6 +1126,11 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Searchers+1956+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1088,6 +1169,11 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=La+Dolce+Vita+1960+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1126,6 +1212,11 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Taxi+Driver+1976+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1164,6 +1255,11 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Rules+of+the+Game+1939+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1202,6 +1298,11 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Do+the+Right+Thing+1989+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1240,6 +1341,11 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Red+Shoes+1948+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1278,6 +1384,11 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Raging+Bull+1980+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1316,6 +1427,11 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Passion+of+Joan+of+Arc+1928+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1354,6 +1470,11 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=8%C2%BD+1963+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1392,6 +1513,11 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Persona+1966+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1430,6 +1556,11 @@
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Bicycle+Thieves+1948+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1468,6 +1599,11 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Lawrence+of+Arabia+1962+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1506,6 +1642,11 @@
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Pulp+Fiction+1994+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1544,6 +1685,11 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Goodfellas+1990+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1582,6 +1728,11 @@
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Shawshank+Redemption+1994+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1620,6 +1771,11 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Dark+Knight+2008+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1658,6 +1814,11 @@
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=No+Country+for+Old+Men+2007+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1696,6 +1857,11 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=There+Will+Be+Blood+2007+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1734,6 +1900,11 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Parasite+2019+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1772,6 +1943,11 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Mad+Max%3A+Fury+Road+2015+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1810,6 +1986,11 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Matrix+1999+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1848,6 +2029,11 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Jaws+1975+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1886,6 +2072,11 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Raiders+of+the+Lost+Ark+1981+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1924,6 +2115,11 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Jurassic+Park+1993+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1962,6 +2158,11 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Empire+Strikes+Back+1980+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2000,6 +2201,11 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Lord+of+the+Rings%3A+The+Fellowship+of+the+Ring+2001+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2038,6 +2244,11 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Lord+of+the+Rings%3A+The+Return+of+the+King+2003+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2076,6 +2287,11 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Silence+of+the+Lambs+1991+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2114,6 +2330,11 @@
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Heat+1995+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2152,6 +2373,11 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Fight+Club+1999+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2190,6 +2416,11 @@
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Social+Network+2010+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2228,6 +2459,11 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Whiplash+2014+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2266,6 +2502,11 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Eternal+Sunshine+of+the+Spotless+Mind+2004+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2304,6 +2545,11 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Children+of+Men+2006+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2342,6 +2588,11 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Arrival+2016+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2380,6 +2631,11 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Interstellar+2014+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2418,6 +2674,11 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Blade+Runner+1982+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2456,6 +2717,11 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=City+of+God+2002+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2494,6 +2760,11 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Oldboy+2003+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2532,6 +2803,11 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Spirited+Away+2001+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2570,6 +2846,11 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Princess+Mononoke+1997+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2608,6 +2889,11 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=La+Haine+1995+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2646,6 +2932,11 @@
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Cinema+Paradiso+1988+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2684,6 +2975,11 @@
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Pan%E2%80%99s+Labyrinth+2006+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2722,6 +3018,11 @@
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Lives+of+Others+2006+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2760,6 +3061,11 @@
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Am%C3%A9lie+2001+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2798,6 +3104,11 @@
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Beau+Travail+1999+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2836,6 +3147,11 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Close-Up+1990+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2874,6 +3190,11 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=A+Brighter+Summer+Day+1991+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2912,6 +3233,11 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Yi+Yi+2000+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2950,6 +3276,11 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Stalker+1979+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2988,6 +3319,11 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Mirror+1975+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3026,6 +3362,11 @@
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Andrei+Rublev+1966+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3064,6 +3405,11 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Playtime+1967+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3102,6 +3448,11 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Battle+of+Algiers+1966+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3140,6 +3491,11 @@
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=M+1931+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3178,6 +3534,11 @@
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Metropolis+1927+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3216,6 +3577,11 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Sunrise%3A+A+Song+of+Two+Humans+1927+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3254,6 +3620,11 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=City+Lights+1931+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3292,6 +3663,11 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Modern+Times+1936+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3330,6 +3706,11 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Some+Like+It+Hot+1959+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3368,6 +3749,11 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Apartment+1960+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3406,6 +3792,11 @@
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Alien+1979+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3444,6 +3835,11 @@
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Aliens+1986+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3482,6 +3878,11 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Thing+1982+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3520,6 +3921,11 @@
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Shining+1980+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3558,6 +3964,11 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Psycho+1960+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3596,6 +4007,11 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Halloween+1978+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3634,6 +4050,11 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Exorcist+1973+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3672,6 +4093,11 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Get+Out+2017+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3710,6 +4136,11 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Fargo+1996+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3748,6 +4179,11 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Big+Lebowski+1998+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3786,6 +4222,11 @@
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Before+Sunrise+1995+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3824,6 +4265,11 @@
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Before+Sunset+2004+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3862,6 +4308,11 @@
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Before+Midnight+2013+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3900,6 +4351,11 @@
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Moonlight+2016+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3938,6 +4394,11 @@
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Her+2013+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3976,6 +4437,11 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Lost+in+Translation+2003+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4014,6 +4480,11 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Grand+Budapest+Hotel+2014+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4052,6 +4523,11 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Oppenheimer+2023+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4090,6 +4566,11 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Dune%3A+Part+Two+2024+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4128,6 +4609,11 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Everything+Everywhere+All+at+Once+2022+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4166,6 +4652,11 @@
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Portrait+of+a+Lady+on+Fire+2019+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4204,6 +4695,11 @@
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=12+Angry+Men+1957+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4242,6 +4738,11 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Schindler%E2%80%99s+List+1993+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4280,6 +4781,11 @@
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=Saving+Private+Ryan+1998+IMDb</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4318,6 +4824,11 @@
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/find/?q=The+Truman+Show+1998+IMDb</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
